--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N70_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N70_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>88.02833438343013</v>
+        <v>14.3046043373074</v>
       </c>
       <c r="D2" t="n">
-        <v>46.81559495950995</v>
+        <v>7.607534180920367</v>
       </c>
       <c r="E2" t="n">
-        <v>27.93370178273248</v>
+        <v>4.539226539694027</v>
       </c>
       <c r="F2" t="n">
-        <v>11.34348546203294</v>
+        <v>1.843316387580354</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>66.47144932269968</v>
+        <v>10.8016105149387</v>
       </c>
       <c r="D3" t="n">
-        <v>34.05873987714983</v>
+        <v>5.534545230036848</v>
       </c>
       <c r="E3" t="n">
-        <v>27.93370178273248</v>
+        <v>4.539226539694027</v>
       </c>
       <c r="F3" t="n">
-        <v>11.34348546203294</v>
+        <v>1.843316387580354</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>24.68837902795114</v>
+        <v>4.011861592042061</v>
       </c>
       <c r="D4" t="n">
-        <v>24.84923317424555</v>
+        <v>4.038000390814902</v>
       </c>
       <c r="E4" t="n">
-        <v>27.93370178273248</v>
+        <v>4.539226539694027</v>
       </c>
       <c r="F4" t="n">
-        <v>11.34348546203294</v>
+        <v>1.843316387580354</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>19.89970458672829</v>
+        <v>3.233701995343347</v>
       </c>
       <c r="D5" t="n">
-        <v>19.05179590288339</v>
+        <v>3.095916834218551</v>
       </c>
       <c r="E5" t="n">
-        <v>27.93370178273248</v>
+        <v>4.539226539694027</v>
       </c>
       <c r="F5" t="n">
-        <v>11.34348546203294</v>
+        <v>1.843316387580354</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.55858759743518</v>
+        <v>4.315770484583217</v>
       </c>
       <c r="D6" t="n">
-        <v>25.72817894273103</v>
+        <v>4.180829078193793</v>
       </c>
       <c r="E6" t="n">
-        <v>27.93370178273248</v>
+        <v>4.539226539694027</v>
       </c>
       <c r="F6" t="n">
-        <v>11.34348546203294</v>
+        <v>1.843316387580354</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>10.7193984130169</v>
+        <v>1.741902242115247</v>
       </c>
       <c r="D7" t="n">
-        <v>10.86888945539967</v>
+        <v>1.766194536502446</v>
       </c>
       <c r="E7" t="n">
-        <v>27.93370178273248</v>
+        <v>4.539226539694027</v>
       </c>
       <c r="F7" t="n">
-        <v>11.34348546203294</v>
+        <v>1.843316387580354</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
